--- a/src/xlsx/ratings.xlsx
+++ b/src/xlsx/ratings.xlsx
@@ -994,6 +994,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>

--- a/src/xlsx/ratings.xlsx
+++ b/src/xlsx/ratings.xlsx
@@ -2226,7 +2226,7 @@
       </c>
       <c r="G52" s="1" t="inlineStr">
         <is>
-          <t>這不是挺不錯的嘛！</t>
+          <t>這不是很不錯嘛！</t>
         </is>
       </c>
       <c r="I52" s="1" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="G65" s="1" t="inlineStr">
         <is>
-          <t>狀態棒棒的！</t>
+          <t>狀態很棒！</t>
         </is>
       </c>
       <c r="I65" s="1" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="G77" s="1" t="inlineStr">
         <is>
-          <t>哎喲喲喲……</t>
+          <t>哎呀呀呀……</t>
         </is>
       </c>
       <c r="I77" s="1" t="inlineStr">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="G104" s="1" t="inlineStr">
         <is>
-          <t>你可以稱得上是個專家嘍！</t>
+          <t>你可以稱得上是個專家囉！</t>
         </is>
       </c>
       <c r="I104" s="1" t="inlineStr">
